--- a/internal_doc/05.测试设计/story/HotSpare/HotSpare.xlsx
+++ b/internal_doc/05.测试设计/story/HotSpare/HotSpare.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="141">
   <si>
     <t>name</t>
   </si>
@@ -179,33 +179,6 @@
   <si>
     <t>1 创建备份节点，rg. getDetail()只返回备份节点A，无其他节点
 2 删除备份节点，rg.getDetail()中无节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>db连到备份节点上插入数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1 创建备份节点A
-2 db=new Sdb()连到备份节点端口上，用db.createCS()创建cs</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1 创建cs时返回错误
-2 db.listCollectionSpaces()返回无cs</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>【待定】</t>
-    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -369,10 +342,6 @@
   <si>
     <t>1 预先删除备份组上的备份节点A
 2 将不存在的节点Aattach进数据组</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>attach失败，返回错误</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -588,33 +557,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">OK，返回-153(组已存在)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>【命令错误时（如removeSpareRG()）,返回-34，集合空间不存在】</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>OK，返回-159（操作只适用于协调节点）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>OK，返回-204（不能删除组内最后一个节点）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>直连到在备份节点上可以创建cscl插入数据</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -682,14 +629,6 @@
   </si>
   <si>
     <t>OK，返回-133（编目节点上找不到组信息）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>直连到数据节点上删除cs,在协调节点查询db.listCollectionSpaces()有cs信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建数据组，在协调节点上创建cs，用db.removeRG()删除数据组，db.listCollectionSpaces()上能查询到cs</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -725,10 +664,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>后面加个用例：回收后的节点attach进另一个数据组</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>删除成功，节点进程停掉，节点文件被删除</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -737,10 +672,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>问建华</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Attach进数据组时节点启动异常</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -750,10 +681,6 @@
   </si>
   <si>
     <t>全量同步完成之前detach节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备份节点数未加上限【还没加用例】</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -763,6 +690,54 @@
   </si>
   <si>
     <t>挂起，未测，开发未明确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jira单</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attach失败，返回错误，getDetail（）中无该节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1 用db.createNode()创建N个不同的备份节点，执行rg.getDetail()验证备份节点是否存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rg.getDetail()中有这N个备份节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建多个不同的备份节点，节点数达到上限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>因开发未定节点上限值，这个用例中的N值未定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OK，返回-153(组已存在)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试用例有问题的，如未测试的，开发未确定的，用荧光黄色标记</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>与预期结果不符的bug，用红色标记</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果开发确定保留数据残留，需要增加一个用例：数据组group1、group2上有数据，备份节点attach进group1，插入数据后，detach出来，又attach进group2，detach出来，又attach进group1，检验三次是否都能数据同步成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>作者：余婷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间：2015-5-20</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -807,15 +782,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -823,11 +804,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -845,6 +841,22 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -868,6 +880,34 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="宋体"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -922,34 +962,6 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="宋体"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1140,31 +1152,31 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I32" tableType="xml" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4" connectionId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I32" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
   <autoFilter ref="A1:I32"/>
   <tableColumns count="9">
-    <tableColumn id="1" uniqueName="name" name="name" dataDxfId="10">
+    <tableColumn id="1" uniqueName="name" name="name" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/@name" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="2" uniqueName="summary" name="summary" dataDxfId="9">
+    <tableColumn id="2" uniqueName="summary" name="summary" dataDxfId="7">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/summary" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="3" uniqueName="preconditions" name="preconditions" dataDxfId="8">
+    <tableColumn id="3" uniqueName="preconditions" name="preconditions" dataDxfId="6">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/preconditions" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="4" uniqueName="execution_type" name="execution_type" dataDxfId="3">
+    <tableColumn id="4" uniqueName="execution_type" name="execution_type" dataDxfId="5">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/execution_type" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="5" uniqueName="importance" name="importance" dataDxfId="2">
+    <tableColumn id="5" uniqueName="importance" name="importance" dataDxfId="4">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/importance" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="6" uniqueName="step_number" name="step_number" dataDxfId="1">
+    <tableColumn id="6" uniqueName="step_number" name="step_number" dataDxfId="3">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/steps/step/step_number" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="7" uniqueName="actions" name="actions" dataDxfId="7">
+    <tableColumn id="7" uniqueName="actions" name="actions" dataDxfId="2">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/steps/step/actions" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="8" uniqueName="expectedresults" name="expectedresults" dataDxfId="6">
+    <tableColumn id="8" uniqueName="expectedresults" name="expectedresults" dataDxfId="1">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/steps/step/expectedresults" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" uniqueName="execution_type" name="execution_type2" dataDxfId="0">
@@ -1471,13 +1483,13 @@
     <col min="6" max="6" width="8.125" style="2" customWidth="1"/>
     <col min="7" max="7" width="38.375" style="2" customWidth="1"/>
     <col min="8" max="8" width="33" style="2" customWidth="1"/>
-    <col min="9" max="9" width="3.625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="6.875" style="2" customWidth="1"/>
     <col min="10" max="10" width="3.25" style="2" customWidth="1"/>
     <col min="11" max="11" width="23.375" style="2" customWidth="1"/>
     <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="67.5">
+    <row r="1" spans="1:12" ht="54">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1506,7 +1518,10 @@
         <v>8</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="81">
@@ -1536,7 +1551,10 @@
         <v>2</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
+      </c>
+      <c r="L2" s="2">
+        <v>863</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="54">
@@ -1567,12 +1585,15 @@
       </c>
       <c r="J3" s="4"/>
       <c r="K3" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
+      </c>
+      <c r="L3" s="2">
+        <v>863</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="54">
       <c r="A4" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1586,7 +1607,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>17</v>
@@ -1596,12 +1617,12 @@
       </c>
       <c r="J4" s="4"/>
       <c r="K4" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="40.5">
       <c r="A5" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="3" t="s">
@@ -1617,22 +1638,25 @@
         <v>1</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I5" s="3">
         <v>2</v>
       </c>
       <c r="J5" s="4"/>
       <c r="K5" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
+      </c>
+      <c r="L5" s="2">
+        <v>863</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="40.5">
       <c r="A6" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="3" t="s">
@@ -1648,22 +1672,25 @@
         <v>1</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I6" s="3">
         <v>2</v>
       </c>
       <c r="J6" s="4"/>
       <c r="K6" s="7" t="s">
-        <v>132</v>
+        <v>123</v>
+      </c>
+      <c r="L6" s="2">
+        <v>864</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="27">
       <c r="A7" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="3" t="s">
@@ -1679,17 +1706,17 @@
         <v>1</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I7" s="3">
         <v>2</v>
       </c>
       <c r="J7" s="4"/>
       <c r="K7" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="81">
@@ -1719,7 +1746,7 @@
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="27">
@@ -1749,7 +1776,7 @@
       </c>
       <c r="J9" s="4"/>
       <c r="K9" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="54">
@@ -1780,12 +1807,12 @@
       </c>
       <c r="J10" s="4"/>
       <c r="K10" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="40.5">
       <c r="A11" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3" t="s">
@@ -1801,17 +1828,17 @@
         <v>1</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I11" s="3">
         <v>2</v>
       </c>
       <c r="J11" s="4"/>
       <c r="K11" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="54">
@@ -1842,7 +1869,7 @@
       </c>
       <c r="J12" s="4"/>
       <c r="K12" s="2" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="54">
@@ -1873,16 +1900,16 @@
       </c>
       <c r="J13" s="4"/>
       <c r="K13" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="54">
-      <c r="A14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="3"/>
+      <c r="A14" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B14" s="6"/>
       <c r="C14" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D14" s="3">
         <v>1</v>
@@ -1894,23 +1921,27 @@
         <v>1</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>34</v>
+        <v>131</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>35</v>
+        <v>132</v>
       </c>
       <c r="I14" s="3">
         <v>2</v>
       </c>
       <c r="J14" s="4"/>
-      <c r="K14" s="2" t="s">
-        <v>95</v>
+      <c r="K14" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="L14" s="2">
+        <v>872</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="54">
       <c r="A15" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B15" s="3"/>
       <c r="C15" s="3" t="s">
         <v>33</v>
       </c>
@@ -1923,59 +1954,56 @@
       <c r="F15" s="2">
         <v>1</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>38</v>
+      <c r="G15" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="I15" s="3">
         <v>2</v>
       </c>
       <c r="J15" s="4"/>
-      <c r="K15" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>133</v>
+      <c r="K15" s="2" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="67.5">
       <c r="A16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="3">
+        <v>1</v>
+      </c>
+      <c r="E16" s="3">
+        <v>2</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D16" s="3">
-        <v>1</v>
-      </c>
-      <c r="E16" s="3">
-        <v>2</v>
-      </c>
-      <c r="F16" s="2">
-        <v>1</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="I16" s="3">
         <v>2</v>
       </c>
       <c r="J16" s="4"/>
       <c r="K16" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="81">
       <c r="A17" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D17" s="3">
         <v>1</v>
@@ -1987,25 +2015,25 @@
         <v>1</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="I17" s="3">
         <v>2</v>
       </c>
       <c r="J17" s="4"/>
       <c r="K17" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="67.5">
       <c r="A18" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D18" s="3">
         <v>1</v>
@@ -2017,55 +2045,55 @@
         <v>1</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I18" s="3">
         <v>2</v>
       </c>
       <c r="J18" s="4"/>
       <c r="K18" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="81">
       <c r="A19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="3">
+        <v>1</v>
+      </c>
+      <c r="E19" s="3">
+        <v>2</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" s="3">
-        <v>1</v>
-      </c>
-      <c r="E19" s="3">
-        <v>2</v>
-      </c>
-      <c r="F19" s="2">
-        <v>1</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="I19" s="3">
         <v>2</v>
       </c>
       <c r="J19" s="4"/>
       <c r="K19" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="108">
       <c r="A20" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D20" s="3">
         <v>1</v>
@@ -2077,85 +2105,85 @@
         <v>1</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I20" s="3">
         <v>2</v>
       </c>
       <c r="J20" s="4"/>
       <c r="K20" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="108">
       <c r="A21" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D21" s="3">
+        <v>1</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H21" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D21" s="3">
-        <v>1</v>
-      </c>
-      <c r="E21" s="3">
-        <v>2</v>
-      </c>
-      <c r="F21" s="2">
-        <v>1</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="I21" s="3">
         <v>2</v>
       </c>
       <c r="J21" s="4"/>
       <c r="K21" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="94.5">
       <c r="A22" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="3">
+        <v>1</v>
+      </c>
+      <c r="E22" s="3">
+        <v>2</v>
+      </c>
+      <c r="F22" s="2">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D22" s="3">
-        <v>1</v>
-      </c>
-      <c r="E22" s="3">
-        <v>2</v>
-      </c>
-      <c r="F22" s="2">
-        <v>1</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="I22" s="3">
         <v>2</v>
       </c>
       <c r="J22" s="4"/>
       <c r="K22" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="94.5">
       <c r="A23" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D23" s="3">
         <v>1</v>
@@ -2167,56 +2195,59 @@
         <v>1</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="I23" s="3">
         <v>2</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>130</v>
+        <v>121</v>
+      </c>
+      <c r="L23" s="2">
+        <v>867</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="67.5">
       <c r="A24" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" s="3">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3">
+        <v>2</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D24" s="3">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3">
-        <v>2</v>
-      </c>
-      <c r="F24" s="2">
-        <v>1</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="H24" s="2" t="s">
-        <v>73</v>
+        <v>130</v>
       </c>
       <c r="I24" s="3">
         <v>2</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>117</v>
+        <v>111</v>
+      </c>
+      <c r="L24" s="2">
+        <v>866</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="67.5">
       <c r="A25" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D25" s="3">
         <v>1</v>
@@ -2228,53 +2259,53 @@
         <v>1</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I25" s="3">
         <v>2</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="81">
       <c r="A26" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D26" s="3">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3">
+        <v>2</v>
+      </c>
+      <c r="F26" s="2">
+        <v>1</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D26" s="3">
-        <v>1</v>
-      </c>
-      <c r="E26" s="3">
-        <v>2</v>
-      </c>
-      <c r="F26" s="2">
-        <v>1</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="I26" s="3">
         <v>2</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="81">
       <c r="A27" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D27" s="3">
         <v>1</v>
@@ -2286,24 +2317,24 @@
         <v>1</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="I27" s="3">
         <v>2</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="67.5">
       <c r="A28" s="2" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D28" s="3">
         <v>1</v>
@@ -2315,24 +2346,27 @@
         <v>1</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="I28" s="3">
         <v>1</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>123</v>
+        <v>117</v>
+      </c>
+      <c r="L28" s="2">
+        <v>868</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="67.5">
       <c r="A29" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D29" s="3">
         <v>1</v>
@@ -2344,103 +2378,109 @@
         <v>1</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="I29" s="3">
         <v>2</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="81">
       <c r="A30" s="2" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C30" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D30" s="3">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3">
+        <v>2</v>
+      </c>
+      <c r="F30" s="2">
+        <v>1</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D30" s="3">
-        <v>1</v>
-      </c>
-      <c r="E30" s="3">
-        <v>2</v>
-      </c>
-      <c r="F30" s="2">
-        <v>1</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="I30" s="3">
         <v>2</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>124</v>
+        <v>118</v>
+      </c>
+      <c r="L30" s="2">
+        <v>869</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="81">
       <c r="A31" s="2" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D31" s="3">
+        <v>1</v>
+      </c>
+      <c r="E31" s="3">
+        <v>2</v>
+      </c>
+      <c r="F31" s="2">
+        <v>1</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D31" s="3">
-        <v>1</v>
-      </c>
-      <c r="E31" s="3">
-        <v>2</v>
-      </c>
-      <c r="F31" s="2">
-        <v>1</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="I31" s="3">
         <v>2</v>
       </c>
-      <c r="K31" s="7" t="s">
-        <v>139</v>
+      <c r="K31" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="L31" s="2">
+        <v>871</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="54">
       <c r="A32" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C32" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D32" s="3">
+        <v>1</v>
+      </c>
+      <c r="E32" s="3">
+        <v>2</v>
+      </c>
+      <c r="F32" s="2">
+        <v>1</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H32" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D32" s="3">
-        <v>1</v>
-      </c>
-      <c r="E32" s="3">
-        <v>2</v>
-      </c>
-      <c r="F32" s="2">
-        <v>1</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="I32" s="3">
         <v>2</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -2467,22 +2507,19 @@
       <c r="I34"/>
       <c r="J34"/>
     </row>
-    <row r="35" spans="1:11" ht="67.5">
+    <row r="35" spans="1:11">
       <c r="A35"/>
       <c r="B35"/>
       <c r="C35"/>
       <c r="D35"/>
       <c r="E35"/>
       <c r="F35"/>
-      <c r="G35" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="H35"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="12" t="s">
+        <v>139</v>
+      </c>
       <c r="I35"/>
       <c r="J35"/>
-      <c r="K35" s="7" t="s">
-        <v>127</v>
-      </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36"/>
@@ -2492,11 +2529,13 @@
       <c r="E36"/>
       <c r="F36"/>
       <c r="G36"/>
-      <c r="H36"/>
+      <c r="H36" s="12" t="s">
+        <v>140</v>
+      </c>
       <c r="I36"/>
       <c r="J36"/>
     </row>
-    <row r="37" spans="1:11" ht="54">
+    <row r="37" spans="1:11">
       <c r="A37"/>
       <c r="B37"/>
       <c r="C37"/>
@@ -2504,14 +2543,14 @@
       <c r="E37"/>
       <c r="F37"/>
       <c r="G37"/>
-      <c r="H37"/>
+      <c r="H37" s="10" t="s">
+        <v>137</v>
+      </c>
       <c r="I37"/>
       <c r="J37"/>
-      <c r="K37" s="7" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11">
+      <c r="K37" s="7"/>
+    </row>
+    <row r="38" spans="1:11" ht="27">
       <c r="A38"/>
       <c r="B38"/>
       <c r="C38"/>
@@ -2519,11 +2558,13 @@
       <c r="E38"/>
       <c r="F38"/>
       <c r="G38"/>
-      <c r="H38"/>
+      <c r="H38" s="11" t="s">
+        <v>136</v>
+      </c>
       <c r="I38"/>
       <c r="J38"/>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" ht="13.5" customHeight="1">
       <c r="A39"/>
       <c r="B39"/>
       <c r="C39"/>
@@ -2532,10 +2573,11 @@
       <c r="F39"/>
       <c r="G39"/>
       <c r="H39"/>
-      <c r="I39"/>
-      <c r="J39"/>
-    </row>
-    <row r="40" spans="1:11">
+      <c r="I39" s="13"/>
+      <c r="J39" s="13"/>
+      <c r="K39" s="13"/>
+    </row>
+    <row r="40" spans="1:11" ht="94.5">
       <c r="A40"/>
       <c r="B40"/>
       <c r="C40"/>
@@ -2543,9 +2585,12 @@
       <c r="E40"/>
       <c r="F40"/>
       <c r="G40"/>
-      <c r="H40"/>
-      <c r="I40"/>
-      <c r="J40"/>
+      <c r="H40" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="I40" s="13"/>
+      <c r="J40" s="13"/>
+      <c r="K40" s="13"/>
     </row>
     <row r="41" spans="1:11">
       <c r="A41"/>
@@ -2555,9 +2600,10 @@
       <c r="E41"/>
       <c r="F41"/>
       <c r="G41"/>
-      <c r="H41"/>
-      <c r="I41"/>
-      <c r="J41"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="13"/>
+      <c r="J41" s="13"/>
+      <c r="K41" s="13"/>
     </row>
     <row r="42" spans="1:11">
       <c r="A42"/>
@@ -2567,7 +2613,7 @@
       <c r="E42"/>
       <c r="F42"/>
       <c r="G42"/>
-      <c r="H42"/>
+      <c r="H42" s="13"/>
       <c r="I42"/>
       <c r="J42"/>
     </row>
@@ -2680,16 +2726,7 @@
       <c r="J51"/>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52"/>
-      <c r="B52"/>
-      <c r="C52"/>
-      <c r="D52"/>
-      <c r="E52"/>
-      <c r="F52"/>
-      <c r="G52"/>
       <c r="H52"/>
-      <c r="I52"/>
-      <c r="J52"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/05.测试设计/story/HotSpare/HotSpare.xlsx
+++ b/internal_doc/05.测试设计/story/HotSpare/HotSpare.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="142">
   <si>
     <t>name</t>
   </si>
@@ -738,6 +738,10 @@
   </si>
   <si>
     <t>时间：2015-5-20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库集群已部署好</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1489,7 +1493,7 @@
     <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="54">
+    <row r="1" spans="1:12" ht="40.5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1596,7 +1600,9 @@
         <v>92</v>
       </c>
       <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
+      <c r="C4" s="3" t="s">
+        <v>141</v>
+      </c>
       <c r="D4" s="3">
         <v>1</v>
       </c>
